--- a/fhir/ig/tei/0.2.2/ValueSet-PueblosOriginariosVS.xlsx
+++ b/fhir/ig/tei/0.2.2/ValueSet-PueblosOriginariosVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T12:08:03-03:00</t>
+    <t>2026-04-30T10:23:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
